--- a/dados/2.xlsx
+++ b/dados/2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BF03A8-AFE6-4734-A37C-93E44A8312E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9D9494-4AFD-44F9-9ABD-A71ED460E793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2754" uniqueCount="67">
   <si>
     <t>Mês</t>
   </si>
@@ -218,6 +218,9 @@
   </si>
   <si>
     <t>MARNEI LIMA MORAIS</t>
+  </si>
+  <si>
+    <t>DAYANE MACLEYNE PEREIRA FREITAS DA SILVA</t>
   </si>
 </sst>
 </file>
@@ -588,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F904"/>
+  <dimension ref="A1:F918"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -599,7 +602,7 @@
     <col min="6" max="6" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -18659,7 +18662,287 @@
         <v>1</v>
       </c>
     </row>
-    <row r="904" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="904" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A904" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B904" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C904" s="4">
+        <v>100</v>
+      </c>
+      <c r="D904" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E904" s="5">
+        <v>37099.751519999998</v>
+      </c>
+      <c r="F904" s="4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="905" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A905" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B905" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C905" s="4">
+        <v>58</v>
+      </c>
+      <c r="D905" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E905" s="5">
+        <v>26482.578020000001</v>
+      </c>
+      <c r="F905" s="4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="906" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A906" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B906" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C906" s="4">
+        <v>129</v>
+      </c>
+      <c r="D906" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E906" s="5">
+        <v>15023.89266</v>
+      </c>
+      <c r="F906" s="4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="907" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A907" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B907" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C907" s="4">
+        <v>81</v>
+      </c>
+      <c r="D907" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E907" s="5">
+        <v>13742.24625</v>
+      </c>
+      <c r="F907" s="4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="908" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A908" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B908" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C908" s="4">
+        <v>95</v>
+      </c>
+      <c r="D908" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E908" s="5">
+        <v>10058.219999999999</v>
+      </c>
+      <c r="F908" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="909" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A909" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B909" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C909" s="4">
+        <v>98</v>
+      </c>
+      <c r="D909" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E909" s="5">
+        <v>6990.1</v>
+      </c>
+      <c r="F909" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="910" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A910" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B910" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C910" s="4">
+        <v>104</v>
+      </c>
+      <c r="D910" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E910" s="5">
+        <v>4628.09</v>
+      </c>
+      <c r="F910" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="911" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A911" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B911" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C911" s="4">
+        <v>6</v>
+      </c>
+      <c r="D911" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E911" s="5">
+        <v>4609.02513</v>
+      </c>
+      <c r="F911" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="912" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A912" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B912" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C912" s="4">
+        <v>85</v>
+      </c>
+      <c r="D912" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E912" s="5">
+        <v>2892.2604999999999</v>
+      </c>
+      <c r="F912" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="913" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A913" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B913" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C913" s="4">
+        <v>34</v>
+      </c>
+      <c r="D913" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E913" s="5">
+        <v>1780.2028800000001</v>
+      </c>
+      <c r="F913" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="914" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A914" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B914" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C914" s="4">
+        <v>137</v>
+      </c>
+      <c r="D914" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E914" s="5">
+        <v>1047.73</v>
+      </c>
+      <c r="F914" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="915" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A915" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B915" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C915" s="4">
+        <v>141</v>
+      </c>
+      <c r="D915" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E915" s="5">
+        <v>307.23</v>
+      </c>
+      <c r="F915" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="916" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A916" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B916" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C916" s="4">
+        <v>1</v>
+      </c>
+      <c r="D916" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E916" s="5">
+        <v>41.97</v>
+      </c>
+      <c r="F916" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="917" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A917" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B917" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C917" s="4">
+        <v>4</v>
+      </c>
+      <c r="D917" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E917" s="5">
+        <v>25.227139999999999</v>
+      </c>
+      <c r="F917" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="918" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
